--- a/Design/Configs/ResourceId.xlsx
+++ b/Design/Configs/ResourceId.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA728425-A1B6-4F9F-BD1F-7725C6747623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-27555" yWindow="1740" windowWidth="28830" windowHeight="15630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>ConfigId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -92,14 +93,18 @@
   </si>
   <si>
     <t>Prefabs/Stars/URPMode/Broken/Prefabs/BrokenPlanet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Stars/URPMode/Black_hole/Black_hole_prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,6 +114,15 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -135,8 +149,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -416,246 +436,261 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.625" customWidth="1"/>
-    <col min="2" max="2" width="67.25" customWidth="1"/>
-    <col min="3" max="3" width="12.5" customWidth="1"/>
-    <col min="4" max="4" width="23.625" customWidth="1"/>
-    <col min="5" max="5" width="11.5" customWidth="1"/>
-    <col min="6" max="6" width="21.125" customWidth="1"/>
-    <col min="7" max="7" width="14.875" customWidth="1"/>
-    <col min="8" max="8" width="16.125" customWidth="1"/>
-    <col min="9" max="9" width="11.875" customWidth="1"/>
-    <col min="10" max="10" width="14.25" customWidth="1"/>
-    <col min="11" max="11" width="17.75" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="16.125" customWidth="1"/>
+    <col min="1" max="1" width="17.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="67.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.25" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14" style="1" customWidth="1"/>
+    <col min="13" max="13" width="16.125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15">
+      <c r="A15" s="1">
         <v>999</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16">
+      <c r="A16" s="1">
         <v>100000</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Design/Configs/ResourceId.xlsx
+++ b/Design/Configs/ResourceId.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA728425-A1B6-4F9F-BD1F-7725C6747623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766282FD-80D3-429E-8133-27C87A58376D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27555" yWindow="1740" windowWidth="28830" windowHeight="15630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="-90" windowWidth="28830" windowHeight="15630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>ConfigId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -96,7 +96,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Prefabs/Stars/URPMode/Black_hole/Black_hole_prefab</t>
+    <t>Prefabs/Treasure/Green_Treasure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Treasure/Orange_Treasure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Treasure/Red_Treasure</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -437,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" style="1" customWidth="1"/>
@@ -694,6 +702,34 @@
         <v>1</v>
       </c>
     </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>15</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
